--- a/Examples/AcPowerSystem/SingleApparatusInfiniteBus/GfmInverterInfiniteBus.xlsx
+++ b/Examples/AcPowerSystem/SingleApparatusInfiniteBus/GfmInverterInfiniteBus.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Power-System-Analysis-Toolbox\Examples\AcPowerSystem\SingleApparatusInfiniteBus\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liao\Desktop\毕业设计\Simplus-Grid-Tool\Examples\AcPowerSystem\SingleApparatusInfiniteBus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ECE420B-1BDE-4F00-AF39-9DFAC6740526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F96DE7B-8173-497A-AC0F-4D2D2B199F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bus" sheetId="1" r:id="rId1"/>
@@ -20,25 +20,17 @@
     <sheet name="Basic" sheetId="4" r:id="rId5"/>
     <sheet name="Advance" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="59">
   <si>
     <t>bus</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -112,10 +104,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>parameters</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Notes:</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -236,6 +224,36 @@
   <si>
     <t>This sheet summarizes the apparatuses connected to buses.</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wLf (pu)</t>
+  </si>
+  <si>
+    <t>Rf (pu)</t>
+  </si>
+  <si>
+    <t>wCf (pu)</t>
+  </si>
+  <si>
+    <t>wLc (pu)</t>
+  </si>
+  <si>
+    <t>Rc (pu)</t>
+  </si>
+  <si>
+    <t>Xov (pu)</t>
+  </si>
+  <si>
+    <t>Droop Dw</t>
+  </si>
+  <si>
+    <t>BW droop (Hz)</t>
+  </si>
+  <si>
+    <t>BW vdq (Hz)</t>
+  </si>
+  <si>
+    <t>BW idq (Hz)</t>
   </si>
 </sst>
 </file>
@@ -315,7 +333,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -599,17 +617,17 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.4">
@@ -644,10 +662,10 @@
         <v>9</v>
       </c>
       <c r="K4" t="s">
+        <v>45</v>
+      </c>
+      <c r="L4" t="s">
         <v>46</v>
-      </c>
-      <c r="L4" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
@@ -705,7 +723,7 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>1E-4</v>
+        <v>0</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -755,12 +773,12 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.4">
@@ -770,8 +788,35 @@
       <c r="B3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>18</v>
+      <c r="C3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I3" t="s">
+        <v>55</v>
+      </c>
+      <c r="J3" t="s">
+        <v>56</v>
+      </c>
+      <c r="K3" t="s">
+        <v>57</v>
+      </c>
+      <c r="L3" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.4">
@@ -805,26 +850,26 @@
         <v>0.02</v>
       </c>
       <c r="F5" s="2">
-        <v>0.01</v>
+        <v>0.3</v>
       </c>
       <c r="G5" s="2">
         <f>F5/5</f>
-        <v>2E-3</v>
+        <v>0.06</v>
       </c>
       <c r="H5" s="2">
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="J5" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K5" s="2">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="L5" s="2">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
@@ -842,22 +887,22 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
@@ -867,7 +912,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
@@ -881,16 +926,16 @@
         <v>12</v>
       </c>
       <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" t="s">
         <v>31</v>
-      </c>
-      <c r="E7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
@@ -923,12 +968,12 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.4">
@@ -951,7 +996,7 @@
         <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
@@ -962,11 +1007,10 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <f>D4/5</f>
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="D4">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -999,17 +1043,17 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B3" s="1">
         <f>B4*1000</f>
@@ -1018,7 +1062,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4" s="2">
         <v>50</v>
@@ -1026,7 +1070,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1034,7 +1078,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1058,17 +1102,17 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -1076,7 +1120,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1084,7 +1128,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1092,7 +1136,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1100,7 +1144,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1108,15 +1152,15 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -1124,23 +1168,23 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B12">
         <v>0</v>

--- a/Examples/AcPowerSystem/SingleApparatusInfiniteBus/GfmInverterInfiniteBus.xlsx
+++ b/Examples/AcPowerSystem/SingleApparatusInfiniteBus/GfmInverterInfiniteBus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liao\Desktop\毕业设计\Simplus-Grid-Tool\Examples\AcPowerSystem\SingleApparatusInfiniteBus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F96DE7B-8173-497A-AC0F-4D2D2B199F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E050031E-3A96-4148-A1AF-A44E5E6B6ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bus" sheetId="1" r:id="rId1"/>
@@ -837,7 +837,7 @@
         <v>2</v>
       </c>
       <c r="B5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="2">
         <v>0.05</v>
@@ -1155,7 +1155,7 @@
         <v>35</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">

--- a/Examples/AcPowerSystem/SingleApparatusInfiniteBus/GfmInverterInfiniteBus.xlsx
+++ b/Examples/AcPowerSystem/SingleApparatusInfiniteBus/GfmInverterInfiniteBus.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Power-System-Analysis-Toolbox\Examples\AcPowerSystem\SingleApparatusInfiniteBus\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Simplus-Grid-Tool-Merge\Simplus-Grid-Tool\Examples\AcPowerSystem\SingleApparatusInfiniteBus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ECE420B-1BDE-4F00-AF39-9DFAC6740526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF981DA3-30E5-4FAC-AD33-6C750CA048CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-90" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bus" sheetId="1" r:id="rId1"/>
@@ -20,18 +20,10 @@
     <sheet name="Basic" sheetId="4" r:id="rId5"/>
     <sheet name="Advance" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -315,7 +307,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>

--- a/Examples/AcPowerSystem/SingleApparatusInfiniteBus/GfmInverterInfiniteBus.xlsx
+++ b/Examples/AcPowerSystem/SingleApparatusInfiniteBus/GfmInverterInfiniteBus.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Simplus-Grid-Tool-Merge\Simplus-Grid-Tool\Examples\AcPowerSystem\SingleApparatusInfiniteBus\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Power-System-Analysis-Toolbox\Examples\AcPowerSystem\SingleApparatusInfiniteBus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF981DA3-30E5-4FAC-AD33-6C750CA048CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ECE420B-1BDE-4F00-AF39-9DFAC6740526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-90" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bus" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,18 @@
     <sheet name="Basic" sheetId="4" r:id="rId5"/>
     <sheet name="Advance" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -307,7 +315,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
